--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202610/Category_P&L_20261007.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202610/Category_P&L_20261007.xlsx
@@ -46741,13 +46741,13 @@
         <v>46302</v>
       </c>
       <c r="B1220">
-        <v>92985678.3</v>
+        <v>94837053.37</v>
       </c>
       <c r="C1220">
-        <v>-662807.7</v>
+        <v>-663088.54</v>
       </c>
       <c r="D1220">
-        <v>-0.006939</v>
+        <v>-0.006942</v>
       </c>
       <c r="E1220">
         <v>-10.8</v>
@@ -46768,10 +46768,10 @@
         <v>0</v>
       </c>
       <c r="K1220">
-        <v>0</v>
+        <v>-4525.72</v>
       </c>
       <c r="L1220">
-        <v>0</v>
+        <v>-4.7E-05</v>
       </c>
     </row>
   </sheetData>
